--- a/Hemapreetha_Timesheet_1June-30June.xlsx
+++ b/Hemapreetha_Timesheet_1June-30June.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gunas\Hema\git-my\vinove\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB3D2254-C2E0-438D-96A8-9F4386D14B69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA6A974E-746C-44FC-82FF-6D5ED4286AD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="37">
   <si>
     <t>Monthly Timesheet</t>
   </si>
@@ -133,6 +133,68 @@
 464481: Plus Documents PT-3097 Creation of new theme (Scottish Widows)
 457974: [PT-2877] - OP - PAI template and theme creation
 Product Backlog Item 501847: +Docs - PT-3508 Aegon -  Amendments to Aegon TargetPlan Factsheet</t>
+  </si>
+  <si>
+    <t>FEFundInfo
+============
+Product Backlog Item 505176: NTAM PRIIPS EU issues
+Product Backlog Item 462523: PT-2701 - Valiant Bank - ESG Report Design Updates</t>
+  </si>
+  <si>
+    <t>FEFundInfo
+============
+Product Backlog Item 499375: +Docs - PT-2348 Phoenix -  Amendments to new TargetDatedFund ESG Factsheet
+Product Backlog Item 505260: Plus Documents PT-3588 Invest Administration A/S - Logo Update
+Product Backlog Item 462523: PT-2701 - Valiant Bank - ESG Report Design Updates
+Product Backlog Item 505176: NTAM PRIIPS EU issues</t>
+  </si>
+  <si>
+    <t>FEFundInfo
+============
+Product Backlog Item 499375: +Docs - PT-2348 Phoenix -  Amendments to new TargetDatedFund ESG Factsheet
+Product Backlog Item 462523: PT-2701 - Valiant Bank - ESG Report Design Updates</t>
+  </si>
+  <si>
+    <t>FEFundInfo
+============
+Product Backlog Item 501857: Plus Documents PT-3525 Risk rating colour change (Zurich Life Assurance plc (Ireland))
+Product Backlog Item 504088: Scottish Widows Digital Rebranding</t>
+  </si>
+  <si>
+    <t>FEFundInfo
+============
+Product Backlog Item 504531: PT-2409 - ZIL Factsheet Migration +Docs - Theme amendments</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FEFundInfo
+============
+Product Backlog Item 504531: PT-2409 - ZIL Factsheet Migration +Docs - Theme amendments 
+Product Backlog Item 505260: Plus Documents PT-3588 Invest Administration A/S - Logo Update </t>
+  </si>
+  <si>
+    <t>FEFundInfo
+============
+Product Backlog Item 504531: PT-2409 - ZIL Factsheet Migration +Docs - Theme amendments - 3
+Product Backlog Item 462523: PT-2701 - Valiant Bank - ESG Report Design Updates - 5</t>
+  </si>
+  <si>
+    <t>FEFundInfo
+============
+Product Backlog Item 499375: +Docs - PT-2348 Phoenix -  Amendments to new TargetDatedFund ESG Factsheet
+Product Backlog Item 504531: PT-2409 - ZIL Factsheet Migration +Docs - Theme amendments</t>
+  </si>
+  <si>
+    <t>FEFundInfo
+============
+Product Backlog Item 504531: PT-2409 - ZIL Factsheet Migration +Docs - Theme amendments
+Product Backlog Item 500669: PT-1998 - Julius Baer New Chart version fix
+Product Backlog Item 501857: Plus Documents PT-3525 Risk rating colour change (Zurich Life Assurance plc (Ireland))</t>
+  </si>
+  <si>
+    <t>FEFundInfo
+============
+Product Backlog Item 504088: Scottish Widows Digital Rebranding
+Product Backlog Item 462462: +Docs - Scottish Widows - ELP - Logo, Font and Colour changes - support work</t>
   </si>
 </sst>
 </file>
@@ -370,15 +432,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="15" fontId="1" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="1" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="1" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="1" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="15" fontId="1" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -387,23 +440,20 @@
     <xf numFmtId="15" fontId="1" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="164" fontId="1" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="3"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="3"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -418,8 +468,20 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="1" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="1" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="1" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -770,15 +832,15 @@
   <sheetData>
     <row r="1" spans="2:9" ht="17.25" thickBot="1"/>
     <row r="2" spans="2:9" ht="59.1" customHeight="1" thickTop="1" thickBot="1">
-      <c r="B2" s="26" t="s">
+      <c r="B2" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
-      <c r="H2" s="28"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="23"/>
     </row>
     <row r="4" spans="2:9" ht="30" customHeight="1">
       <c r="B4" s="3" t="s">
@@ -800,11 +862,11 @@
       <c r="B5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="29">
+      <c r="C5" s="25">
         <v>9025475571</v>
       </c>
-      <c r="D5" s="29"/>
-      <c r="E5" s="29"/>
+      <c r="D5" s="25"/>
+      <c r="E5" s="25"/>
       <c r="G5" s="3" t="s">
         <v>4</v>
       </c>
@@ -816,11 +878,11 @@
       <c r="B6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="30" t="s">
+      <c r="C6" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="30"/>
-      <c r="E6" s="30"/>
+      <c r="D6" s="26"/>
+      <c r="E6" s="26"/>
     </row>
     <row r="8" spans="2:9" ht="30" customHeight="1">
       <c r="B8" s="5" t="s">
@@ -829,13 +891,13 @@
       <c r="C8" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="31" t="s">
+      <c r="D8" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="32"/>
-      <c r="F8" s="32"/>
-      <c r="G8" s="32"/>
-      <c r="H8" s="33"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="29"/>
       <c r="I8" s="7" t="s">
         <v>9</v>
       </c>
@@ -847,13 +909,13 @@
       <c r="C9" s="8">
         <v>0</v>
       </c>
-      <c r="D9" s="20" t="s">
+      <c r="D9" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="E9" s="21"/>
-      <c r="F9" s="21"/>
-      <c r="G9" s="21"/>
-      <c r="H9" s="22"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="18"/>
+      <c r="H9" s="19"/>
       <c r="I9" s="14"/>
     </row>
     <row r="10" spans="2:9" ht="88.5" customHeight="1">
@@ -863,13 +925,13 @@
       <c r="C10" s="8">
         <v>8.5</v>
       </c>
-      <c r="D10" s="20" t="s">
+      <c r="D10" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="E10" s="21"/>
-      <c r="F10" s="21"/>
-      <c r="G10" s="21"/>
-      <c r="H10" s="22"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
+      <c r="G10" s="18"/>
+      <c r="H10" s="19"/>
       <c r="I10" s="14"/>
     </row>
     <row r="11" spans="2:9" ht="72" customHeight="1">
@@ -879,13 +941,13 @@
       <c r="C11" s="8">
         <v>8.5</v>
       </c>
-      <c r="D11" s="34" t="s">
+      <c r="D11" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="E11" s="21"/>
-      <c r="F11" s="21"/>
-      <c r="G11" s="21"/>
-      <c r="H11" s="22"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="18"/>
+      <c r="H11" s="19"/>
       <c r="I11" s="14"/>
     </row>
     <row r="12" spans="2:9" ht="90.75" customHeight="1">
@@ -895,13 +957,13 @@
       <c r="C12" s="8">
         <v>8.5</v>
       </c>
-      <c r="D12" s="20" t="s">
+      <c r="D12" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="E12" s="21"/>
-      <c r="F12" s="21"/>
-      <c r="G12" s="21"/>
-      <c r="H12" s="22"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
+      <c r="G12" s="18"/>
+      <c r="H12" s="19"/>
       <c r="I12" s="14"/>
     </row>
     <row r="13" spans="2:9" ht="72.75" customHeight="1">
@@ -911,13 +973,13 @@
       <c r="C13" s="8">
         <v>8.5</v>
       </c>
-      <c r="D13" s="20" t="s">
+      <c r="D13" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="E13" s="21"/>
-      <c r="F13" s="21"/>
-      <c r="G13" s="21"/>
-      <c r="H13" s="22"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
+      <c r="G13" s="18"/>
+      <c r="H13" s="19"/>
       <c r="I13" s="14"/>
     </row>
     <row r="14" spans="2:9" ht="86.25" customHeight="1">
@@ -927,13 +989,13 @@
       <c r="C14" s="8">
         <v>8.5</v>
       </c>
-      <c r="D14" s="20" t="s">
+      <c r="D14" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="E14" s="21"/>
-      <c r="F14" s="21"/>
-      <c r="G14" s="21"/>
-      <c r="H14" s="22"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="18"/>
+      <c r="G14" s="18"/>
+      <c r="H14" s="19"/>
       <c r="I14" s="14"/>
     </row>
     <row r="15" spans="2:9" ht="17.25" customHeight="1">
@@ -943,13 +1005,13 @@
       <c r="C15" s="8">
         <v>0</v>
       </c>
-      <c r="D15" s="20" t="s">
+      <c r="D15" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="E15" s="21"/>
-      <c r="F15" s="21"/>
-      <c r="G15" s="21"/>
-      <c r="H15" s="22"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="18"/>
+      <c r="H15" s="19"/>
       <c r="I15" s="14"/>
     </row>
     <row r="16" spans="2:9" ht="21" customHeight="1">
@@ -959,13 +1021,13 @@
       <c r="C16" s="8">
         <v>0</v>
       </c>
-      <c r="D16" s="20" t="s">
+      <c r="D16" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="E16" s="21"/>
-      <c r="F16" s="21"/>
-      <c r="G16" s="21"/>
-      <c r="H16" s="22"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="18"/>
+      <c r="G16" s="18"/>
+      <c r="H16" s="19"/>
       <c r="I16" s="14"/>
     </row>
     <row r="17" spans="2:9" ht="18" customHeight="1">
@@ -975,13 +1037,13 @@
       <c r="C17" s="8">
         <v>0</v>
       </c>
-      <c r="D17" s="20" t="s">
+      <c r="D17" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="E17" s="21"/>
-      <c r="F17" s="21"/>
-      <c r="G17" s="21"/>
-      <c r="H17" s="22"/>
+      <c r="E17" s="18"/>
+      <c r="F17" s="18"/>
+      <c r="G17" s="18"/>
+      <c r="H17" s="19"/>
       <c r="I17" s="14"/>
     </row>
     <row r="18" spans="2:9" ht="18" customHeight="1">
@@ -991,13 +1053,13 @@
       <c r="C18" s="8">
         <v>0</v>
       </c>
-      <c r="D18" s="20" t="s">
+      <c r="D18" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="E18" s="21"/>
-      <c r="F18" s="21"/>
-      <c r="G18" s="21"/>
-      <c r="H18" s="22"/>
+      <c r="E18" s="18"/>
+      <c r="F18" s="18"/>
+      <c r="G18" s="18"/>
+      <c r="H18" s="19"/>
       <c r="I18" s="14"/>
     </row>
     <row r="19" spans="2:9" ht="18.75" customHeight="1">
@@ -1007,13 +1069,13 @@
       <c r="C19" s="8">
         <v>0</v>
       </c>
-      <c r="D19" s="20" t="s">
+      <c r="D19" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="E19" s="21"/>
-      <c r="F19" s="21"/>
-      <c r="G19" s="21"/>
-      <c r="H19" s="22"/>
+      <c r="E19" s="18"/>
+      <c r="F19" s="18"/>
+      <c r="G19" s="18"/>
+      <c r="H19" s="19"/>
       <c r="I19" s="14"/>
     </row>
     <row r="20" spans="2:9" ht="18" customHeight="1">
@@ -1023,13 +1085,13 @@
       <c r="C20" s="8">
         <v>0</v>
       </c>
-      <c r="D20" s="20" t="s">
+      <c r="D20" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="E20" s="21"/>
-      <c r="F20" s="21"/>
-      <c r="G20" s="21"/>
-      <c r="H20" s="22"/>
+      <c r="E20" s="18"/>
+      <c r="F20" s="18"/>
+      <c r="G20" s="18"/>
+      <c r="H20" s="19"/>
       <c r="I20" s="14"/>
     </row>
     <row r="21" spans="2:9" ht="18.75" customHeight="1">
@@ -1039,13 +1101,13 @@
       <c r="C21" s="8">
         <v>0</v>
       </c>
-      <c r="D21" s="20" t="s">
+      <c r="D21" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="E21" s="21"/>
-      <c r="F21" s="21"/>
-      <c r="G21" s="21"/>
-      <c r="H21" s="22"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="18"/>
+      <c r="G21" s="18"/>
+      <c r="H21" s="19"/>
       <c r="I21" s="14"/>
     </row>
     <row r="22" spans="2:9" ht="21.75" customHeight="1">
@@ -1055,13 +1117,13 @@
       <c r="C22" s="8">
         <v>0</v>
       </c>
-      <c r="D22" s="20" t="s">
+      <c r="D22" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="E22" s="21"/>
-      <c r="F22" s="21"/>
-      <c r="G22" s="21"/>
-      <c r="H22" s="22"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="18"/>
+      <c r="H22" s="19"/>
       <c r="I22" s="14"/>
     </row>
     <row r="23" spans="2:9" ht="21" customHeight="1">
@@ -1071,193 +1133,253 @@
       <c r="C23" s="8">
         <v>0</v>
       </c>
-      <c r="D23" s="20" t="s">
+      <c r="D23" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="E23" s="21"/>
-      <c r="F23" s="21"/>
-      <c r="G23" s="21"/>
-      <c r="H23" s="22"/>
+      <c r="E23" s="18"/>
+      <c r="F23" s="18"/>
+      <c r="G23" s="18"/>
+      <c r="H23" s="19"/>
       <c r="I23" s="14"/>
     </row>
-    <row r="24" spans="2:9" ht="29.25" customHeight="1">
+    <row r="24" spans="2:9" ht="75" customHeight="1">
       <c r="B24" s="7">
         <v>45824</v>
       </c>
-      <c r="C24" s="8"/>
-      <c r="D24" s="20"/>
-      <c r="E24" s="21"/>
-      <c r="F24" s="21"/>
-      <c r="G24" s="21"/>
-      <c r="H24" s="22"/>
+      <c r="C24" s="8">
+        <v>8.5</v>
+      </c>
+      <c r="D24" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="E24" s="18"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="18"/>
+      <c r="H24" s="19"/>
       <c r="I24" s="14"/>
     </row>
-    <row r="25" spans="2:9" ht="22.5" customHeight="1">
+    <row r="25" spans="2:9" ht="104.25" customHeight="1">
       <c r="B25" s="7">
         <v>45825</v>
       </c>
-      <c r="C25" s="8"/>
-      <c r="D25" s="20"/>
-      <c r="E25" s="21"/>
-      <c r="F25" s="21"/>
-      <c r="G25" s="21"/>
-      <c r="H25" s="22"/>
+      <c r="C25" s="8">
+        <v>8.5</v>
+      </c>
+      <c r="D25" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="E25" s="18"/>
+      <c r="F25" s="18"/>
+      <c r="G25" s="18"/>
+      <c r="H25" s="19"/>
       <c r="I25" s="14"/>
     </row>
-    <row r="26" spans="2:9" ht="23.25" customHeight="1">
+    <row r="26" spans="2:9" ht="69" customHeight="1">
       <c r="B26" s="7">
         <v>45826</v>
       </c>
-      <c r="C26" s="8"/>
-      <c r="D26" s="20"/>
-      <c r="E26" s="21"/>
-      <c r="F26" s="21"/>
-      <c r="G26" s="21"/>
-      <c r="H26" s="22"/>
+      <c r="C26" s="8">
+        <v>8.5</v>
+      </c>
+      <c r="D26" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="E26" s="18"/>
+      <c r="F26" s="18"/>
+      <c r="G26" s="18"/>
+      <c r="H26" s="19"/>
       <c r="I26" s="14"/>
     </row>
-    <row r="27" spans="2:9" ht="30" customHeight="1">
+    <row r="27" spans="2:9" ht="72.75" customHeight="1">
       <c r="B27" s="7">
         <v>45827</v>
       </c>
-      <c r="C27" s="8"/>
-      <c r="D27" s="20"/>
-      <c r="E27" s="21"/>
-      <c r="F27" s="21"/>
-      <c r="G27" s="21"/>
-      <c r="H27" s="22"/>
+      <c r="C27" s="8">
+        <v>8.5</v>
+      </c>
+      <c r="D27" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E27" s="18"/>
+      <c r="F27" s="18"/>
+      <c r="G27" s="18"/>
+      <c r="H27" s="19"/>
       <c r="I27" s="14"/>
     </row>
-    <row r="28" spans="2:9" ht="33" customHeight="1">
+    <row r="28" spans="2:9" ht="69.75" customHeight="1">
       <c r="B28" s="7">
         <v>45828</v>
       </c>
-      <c r="C28" s="8"/>
-      <c r="D28" s="20"/>
-      <c r="E28" s="21"/>
-      <c r="F28" s="21"/>
-      <c r="G28" s="21"/>
-      <c r="H28" s="22"/>
+      <c r="C28" s="8">
+        <v>8.5</v>
+      </c>
+      <c r="D28" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E28" s="18"/>
+      <c r="F28" s="18"/>
+      <c r="G28" s="18"/>
+      <c r="H28" s="19"/>
       <c r="I28" s="14"/>
     </row>
-    <row r="29" spans="2:9" ht="28.5" customHeight="1">
+    <row r="29" spans="2:9" ht="18.75" customHeight="1">
       <c r="B29" s="7">
         <v>45829</v>
       </c>
-      <c r="C29" s="8"/>
-      <c r="D29" s="20"/>
-      <c r="E29" s="21"/>
-      <c r="F29" s="21"/>
-      <c r="G29" s="21"/>
-      <c r="H29" s="22"/>
+      <c r="C29" s="8">
+        <v>0</v>
+      </c>
+      <c r="D29" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="E29" s="18"/>
+      <c r="F29" s="18"/>
+      <c r="G29" s="18"/>
+      <c r="H29" s="19"/>
       <c r="I29" s="14"/>
     </row>
-    <row r="30" spans="2:9" ht="30" customHeight="1">
+    <row r="30" spans="2:9" ht="21.75" customHeight="1">
       <c r="B30" s="7">
         <v>45830</v>
       </c>
-      <c r="C30" s="8"/>
-      <c r="D30" s="20"/>
-      <c r="E30" s="21"/>
-      <c r="F30" s="21"/>
-      <c r="G30" s="21"/>
-      <c r="H30" s="22"/>
+      <c r="C30" s="8">
+        <v>0</v>
+      </c>
+      <c r="D30" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="E30" s="18"/>
+      <c r="F30" s="18"/>
+      <c r="G30" s="18"/>
+      <c r="H30" s="19"/>
       <c r="I30" s="14"/>
     </row>
-    <row r="31" spans="2:9" ht="25.5" customHeight="1">
+    <row r="31" spans="2:9" ht="65.25" customHeight="1">
       <c r="B31" s="7">
         <v>45831</v>
       </c>
-      <c r="C31" s="8"/>
-      <c r="D31" s="20"/>
-      <c r="E31" s="21"/>
-      <c r="F31" s="21"/>
-      <c r="G31" s="21"/>
-      <c r="H31" s="22"/>
+      <c r="C31" s="8">
+        <v>8.5</v>
+      </c>
+      <c r="D31" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="E31" s="18"/>
+      <c r="F31" s="18"/>
+      <c r="G31" s="18"/>
+      <c r="H31" s="19"/>
       <c r="I31" s="14"/>
     </row>
-    <row r="32" spans="2:9" ht="23.25" customHeight="1">
+    <row r="32" spans="2:9" ht="76.5" customHeight="1">
       <c r="B32" s="7">
         <v>45832</v>
       </c>
-      <c r="C32" s="8"/>
-      <c r="D32" s="20"/>
-      <c r="E32" s="21"/>
-      <c r="F32" s="21"/>
-      <c r="G32" s="21"/>
-      <c r="H32" s="22"/>
+      <c r="C32" s="8">
+        <v>8.5</v>
+      </c>
+      <c r="D32" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="E32" s="18"/>
+      <c r="F32" s="18"/>
+      <c r="G32" s="18"/>
+      <c r="H32" s="19"/>
       <c r="I32" s="14"/>
     </row>
-    <row r="33" spans="2:9" ht="22.5" customHeight="1">
+    <row r="33" spans="2:9" ht="78" customHeight="1">
       <c r="B33" s="7">
         <v>45833</v>
       </c>
-      <c r="C33" s="8"/>
-      <c r="D33" s="20"/>
-      <c r="E33" s="21"/>
-      <c r="F33" s="21"/>
-      <c r="G33" s="21"/>
-      <c r="H33" s="22"/>
+      <c r="C33" s="8">
+        <v>8.5</v>
+      </c>
+      <c r="D33" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="E33" s="18"/>
+      <c r="F33" s="18"/>
+      <c r="G33" s="18"/>
+      <c r="H33" s="19"/>
       <c r="I33" s="14"/>
     </row>
-    <row r="34" spans="2:9" ht="25.5" customHeight="1">
+    <row r="34" spans="2:9" ht="79.5" customHeight="1">
       <c r="B34" s="7">
         <v>45834</v>
       </c>
-      <c r="C34" s="8"/>
-      <c r="D34" s="20"/>
-      <c r="E34" s="21"/>
-      <c r="F34" s="21"/>
-      <c r="G34" s="21"/>
-      <c r="H34" s="22"/>
+      <c r="C34" s="8">
+        <v>8.5</v>
+      </c>
+      <c r="D34" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="E34" s="18"/>
+      <c r="F34" s="18"/>
+      <c r="G34" s="18"/>
+      <c r="H34" s="19"/>
       <c r="I34" s="14"/>
     </row>
-    <row r="35" spans="2:9" ht="24.75" customHeight="1">
+    <row r="35" spans="2:9" ht="93" customHeight="1">
       <c r="B35" s="7">
         <v>45835</v>
       </c>
-      <c r="C35" s="8"/>
-      <c r="D35" s="20"/>
-      <c r="E35" s="21"/>
-      <c r="F35" s="21"/>
-      <c r="G35" s="21"/>
-      <c r="H35" s="22"/>
+      <c r="C35" s="8">
+        <v>8.5</v>
+      </c>
+      <c r="D35" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="E35" s="18"/>
+      <c r="F35" s="18"/>
+      <c r="G35" s="18"/>
+      <c r="H35" s="19"/>
       <c r="I35" s="14"/>
     </row>
     <row r="36" spans="2:9" ht="24.75" customHeight="1">
       <c r="B36" s="7">
         <v>45836</v>
       </c>
-      <c r="C36" s="8"/>
-      <c r="D36" s="20"/>
-      <c r="E36" s="21"/>
-      <c r="F36" s="21"/>
-      <c r="G36" s="21"/>
-      <c r="H36" s="22"/>
+      <c r="C36" s="8">
+        <v>0</v>
+      </c>
+      <c r="D36" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="E36" s="18"/>
+      <c r="F36" s="18"/>
+      <c r="G36" s="18"/>
+      <c r="H36" s="19"/>
       <c r="I36" s="14"/>
     </row>
     <row r="37" spans="2:9" ht="28.5" customHeight="1">
       <c r="B37" s="7">
         <v>45837</v>
       </c>
-      <c r="C37" s="8"/>
-      <c r="D37" s="17"/>
-      <c r="E37" s="18"/>
-      <c r="F37" s="18"/>
-      <c r="G37" s="18"/>
-      <c r="H37" s="19"/>
+      <c r="C37" s="8">
+        <v>0</v>
+      </c>
+      <c r="D37" s="32" t="s">
+        <v>17</v>
+      </c>
+      <c r="E37" s="33"/>
+      <c r="F37" s="33"/>
+      <c r="G37" s="33"/>
+      <c r="H37" s="34"/>
       <c r="I37" s="14"/>
     </row>
-    <row r="38" spans="2:9" ht="28.5" customHeight="1">
+    <row r="38" spans="2:9" ht="74.25" customHeight="1">
       <c r="B38" s="7">
         <v>45838</v>
       </c>
-      <c r="C38" s="8"/>
-      <c r="D38" s="17"/>
-      <c r="E38" s="18"/>
-      <c r="F38" s="18"/>
-      <c r="G38" s="18"/>
-      <c r="H38" s="19"/>
+      <c r="C38" s="8">
+        <v>8.5</v>
+      </c>
+      <c r="D38" s="32" t="s">
+        <v>36</v>
+      </c>
+      <c r="E38" s="33"/>
+      <c r="F38" s="33"/>
+      <c r="G38" s="33"/>
+      <c r="H38" s="34"/>
       <c r="I38" s="14"/>
     </row>
     <row r="39" spans="2:9" ht="30" customHeight="1">
@@ -1266,21 +1388,21 @@
       </c>
       <c r="C39" s="10">
         <f>SUM(C9:C38)</f>
-        <v>42.5</v>
-      </c>
-      <c r="D39" s="25" t="s">
+        <v>136</v>
+      </c>
+      <c r="D39" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="E39" s="25"/>
-      <c r="F39" s="25"/>
-      <c r="G39" s="25"/>
-      <c r="H39" s="25"/>
+      <c r="E39" s="31"/>
+      <c r="F39" s="31"/>
+      <c r="G39" s="31"/>
+      <c r="H39" s="31"/>
     </row>
     <row r="41" spans="2:9" ht="30" customHeight="1">
-      <c r="B41" s="23" t="s">
+      <c r="B41" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="C41" s="23"/>
+      <c r="C41" s="30"/>
       <c r="D41" s="24"/>
       <c r="E41" s="24"/>
       <c r="F41" s="24"/>
@@ -1295,10 +1417,10 @@
       <c r="B42" s="12"/>
     </row>
     <row r="43" spans="2:9" ht="30" customHeight="1">
-      <c r="B43" s="23" t="s">
+      <c r="B43" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="C43" s="23"/>
+      <c r="C43" s="30"/>
       <c r="D43" s="24"/>
       <c r="E43" s="24"/>
       <c r="F43" s="24"/>
@@ -1311,10 +1433,10 @@
       <c r="B44" s="12"/>
     </row>
     <row r="45" spans="2:9" ht="30" customHeight="1">
-      <c r="B45" s="23" t="s">
+      <c r="B45" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="C45" s="23"/>
+      <c r="C45" s="30"/>
       <c r="D45" s="24"/>
       <c r="E45" s="24"/>
       <c r="F45" s="24"/>
@@ -1325,32 +1447,6 @@
     </row>
   </sheetData>
   <mergeCells count="42">
-    <mergeCell ref="D27:H27"/>
-    <mergeCell ref="D17:H17"/>
-    <mergeCell ref="D18:H18"/>
-    <mergeCell ref="D19:H19"/>
-    <mergeCell ref="D20:H20"/>
-    <mergeCell ref="D21:H21"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="D16:H16"/>
-    <mergeCell ref="D10:H10"/>
-    <mergeCell ref="D11:H11"/>
-    <mergeCell ref="D12:H12"/>
-    <mergeCell ref="D13:H13"/>
-    <mergeCell ref="D14:H14"/>
-    <mergeCell ref="D9:H9"/>
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="C4:E4"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="D8:H8"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="D43:F43"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="D45:F45"/>
-    <mergeCell ref="D39:H39"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="D41:F41"/>
     <mergeCell ref="D38:H38"/>
     <mergeCell ref="D28:H28"/>
     <mergeCell ref="D29:H29"/>
@@ -1367,6 +1463,32 @@
     <mergeCell ref="D37:H37"/>
     <mergeCell ref="D25:H25"/>
     <mergeCell ref="D26:H26"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="D43:F43"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="D45:F45"/>
+    <mergeCell ref="D39:H39"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="D41:F41"/>
+    <mergeCell ref="D9:H9"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="D8:H8"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="D16:H16"/>
+    <mergeCell ref="D10:H10"/>
+    <mergeCell ref="D11:H11"/>
+    <mergeCell ref="D12:H12"/>
+    <mergeCell ref="D13:H13"/>
+    <mergeCell ref="D14:H14"/>
+    <mergeCell ref="D27:H27"/>
+    <mergeCell ref="D17:H17"/>
+    <mergeCell ref="D18:H18"/>
+    <mergeCell ref="D19:H19"/>
+    <mergeCell ref="D20:H20"/>
+    <mergeCell ref="D21:H21"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <hyperlinks>
@@ -1380,12 +1502,9 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1503,15 +1622,19 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3DBB90D6-6CF2-454A-903E-412076510F41}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2557F9BC-8CE0-4467-BBA0-44089D18E7E7}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1533,10 +1656,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2557F9BC-8CE0-4467-BBA0-44089D18E7E7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3DBB90D6-6CF2-454A-903E-412076510F41}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Hemapreetha_Timesheet_1June-30June.xlsx
+++ b/Hemapreetha_Timesheet_1June-30June.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gunas\Hema\git-my\vinove\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA6A974E-746C-44FC-82FF-6D5ED4286AD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{801A7756-0FBF-45C7-B5DF-AE922CE38056}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -174,12 +174,6 @@
   <si>
     <t>FEFundInfo
 ============
-Product Backlog Item 504531: PT-2409 - ZIL Factsheet Migration +Docs - Theme amendments - 3
-Product Backlog Item 462523: PT-2701 - Valiant Bank - ESG Report Design Updates - 5</t>
-  </si>
-  <si>
-    <t>FEFundInfo
-============
 Product Backlog Item 499375: +Docs - PT-2348 Phoenix -  Amendments to new TargetDatedFund ESG Factsheet
 Product Backlog Item 504531: PT-2409 - ZIL Factsheet Migration +Docs - Theme amendments</t>
   </si>
@@ -195,6 +189,12 @@
 ============
 Product Backlog Item 504088: Scottish Widows Digital Rebranding
 Product Backlog Item 462462: +Docs - Scottish Widows - ELP - Logo, Font and Colour changes - support work</t>
+  </si>
+  <si>
+    <t>FEFundInfo
+============
+Product Backlog Item 504531: PT-2409 - ZIL Factsheet Migration +Docs - Theme amendments
+Product Backlog Item 462523: PT-2701 - Valiant Bank - ESG Report Design Updates</t>
   </si>
 </sst>
 </file>
@@ -432,6 +432,15 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="15" fontId="1" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="1" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="1" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="1" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="15" fontId="1" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -440,8 +449,14 @@
     <xf numFmtId="15" fontId="1" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="3"/>
@@ -451,9 +466,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -468,20 +480,8 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="1" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="1" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="1" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="164" fontId="1" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -832,15 +832,15 @@
   <sheetData>
     <row r="1" spans="2:9" ht="17.25" thickBot="1"/>
     <row r="2" spans="2:9" ht="59.1" customHeight="1" thickTop="1" thickBot="1">
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="23"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="28"/>
     </row>
     <row r="4" spans="2:9" ht="30" customHeight="1">
       <c r="B4" s="3" t="s">
@@ -862,11 +862,11 @@
       <c r="B5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="25">
+      <c r="C5" s="29">
         <v>9025475571</v>
       </c>
-      <c r="D5" s="25"/>
-      <c r="E5" s="25"/>
+      <c r="D5" s="29"/>
+      <c r="E5" s="29"/>
       <c r="G5" s="3" t="s">
         <v>4</v>
       </c>
@@ -878,11 +878,11 @@
       <c r="B6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="26" t="s">
+      <c r="C6" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="26"/>
-      <c r="E6" s="26"/>
+      <c r="D6" s="30"/>
+      <c r="E6" s="30"/>
     </row>
     <row r="8" spans="2:9" ht="30" customHeight="1">
       <c r="B8" s="5" t="s">
@@ -891,13 +891,13 @@
       <c r="C8" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="27" t="s">
+      <c r="D8" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="28"/>
-      <c r="F8" s="28"/>
-      <c r="G8" s="28"/>
-      <c r="H8" s="29"/>
+      <c r="E8" s="32"/>
+      <c r="F8" s="32"/>
+      <c r="G8" s="32"/>
+      <c r="H8" s="33"/>
       <c r="I8" s="7" t="s">
         <v>9</v>
       </c>
@@ -909,13 +909,13 @@
       <c r="C9" s="8">
         <v>0</v>
       </c>
-      <c r="D9" s="17" t="s">
+      <c r="D9" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="E9" s="18"/>
-      <c r="F9" s="18"/>
-      <c r="G9" s="18"/>
-      <c r="H9" s="19"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="21"/>
+      <c r="G9" s="21"/>
+      <c r="H9" s="22"/>
       <c r="I9" s="14"/>
     </row>
     <row r="10" spans="2:9" ht="88.5" customHeight="1">
@@ -925,13 +925,13 @@
       <c r="C10" s="8">
         <v>8.5</v>
       </c>
-      <c r="D10" s="17" t="s">
+      <c r="D10" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="E10" s="18"/>
-      <c r="F10" s="18"/>
-      <c r="G10" s="18"/>
-      <c r="H10" s="19"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="21"/>
+      <c r="G10" s="21"/>
+      <c r="H10" s="22"/>
       <c r="I10" s="14"/>
     </row>
     <row r="11" spans="2:9" ht="72" customHeight="1">
@@ -941,13 +941,13 @@
       <c r="C11" s="8">
         <v>8.5</v>
       </c>
-      <c r="D11" s="20" t="s">
+      <c r="D11" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
-      <c r="G11" s="18"/>
-      <c r="H11" s="19"/>
+      <c r="E11" s="21"/>
+      <c r="F11" s="21"/>
+      <c r="G11" s="21"/>
+      <c r="H11" s="22"/>
       <c r="I11" s="14"/>
     </row>
     <row r="12" spans="2:9" ht="90.75" customHeight="1">
@@ -957,13 +957,13 @@
       <c r="C12" s="8">
         <v>8.5</v>
       </c>
-      <c r="D12" s="17" t="s">
+      <c r="D12" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="E12" s="18"/>
-      <c r="F12" s="18"/>
-      <c r="G12" s="18"/>
-      <c r="H12" s="19"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="21"/>
+      <c r="G12" s="21"/>
+      <c r="H12" s="22"/>
       <c r="I12" s="14"/>
     </row>
     <row r="13" spans="2:9" ht="72.75" customHeight="1">
@@ -973,13 +973,13 @@
       <c r="C13" s="8">
         <v>8.5</v>
       </c>
-      <c r="D13" s="17" t="s">
+      <c r="D13" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18"/>
-      <c r="G13" s="18"/>
-      <c r="H13" s="19"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="21"/>
+      <c r="G13" s="21"/>
+      <c r="H13" s="22"/>
       <c r="I13" s="14"/>
     </row>
     <row r="14" spans="2:9" ht="86.25" customHeight="1">
@@ -989,13 +989,13 @@
       <c r="C14" s="8">
         <v>8.5</v>
       </c>
-      <c r="D14" s="17" t="s">
+      <c r="D14" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="E14" s="18"/>
-      <c r="F14" s="18"/>
-      <c r="G14" s="18"/>
-      <c r="H14" s="19"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="21"/>
+      <c r="G14" s="21"/>
+      <c r="H14" s="22"/>
       <c r="I14" s="14"/>
     </row>
     <row r="15" spans="2:9" ht="17.25" customHeight="1">
@@ -1005,13 +1005,13 @@
       <c r="C15" s="8">
         <v>0</v>
       </c>
-      <c r="D15" s="17" t="s">
+      <c r="D15" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="E15" s="18"/>
-      <c r="F15" s="18"/>
-      <c r="G15" s="18"/>
-      <c r="H15" s="19"/>
+      <c r="E15" s="21"/>
+      <c r="F15" s="21"/>
+      <c r="G15" s="21"/>
+      <c r="H15" s="22"/>
       <c r="I15" s="14"/>
     </row>
     <row r="16" spans="2:9" ht="21" customHeight="1">
@@ -1021,13 +1021,13 @@
       <c r="C16" s="8">
         <v>0</v>
       </c>
-      <c r="D16" s="17" t="s">
+      <c r="D16" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="E16" s="18"/>
-      <c r="F16" s="18"/>
-      <c r="G16" s="18"/>
-      <c r="H16" s="19"/>
+      <c r="E16" s="21"/>
+      <c r="F16" s="21"/>
+      <c r="G16" s="21"/>
+      <c r="H16" s="22"/>
       <c r="I16" s="14"/>
     </row>
     <row r="17" spans="2:9" ht="18" customHeight="1">
@@ -1037,13 +1037,13 @@
       <c r="C17" s="8">
         <v>0</v>
       </c>
-      <c r="D17" s="17" t="s">
+      <c r="D17" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="E17" s="18"/>
-      <c r="F17" s="18"/>
-      <c r="G17" s="18"/>
-      <c r="H17" s="19"/>
+      <c r="E17" s="21"/>
+      <c r="F17" s="21"/>
+      <c r="G17" s="21"/>
+      <c r="H17" s="22"/>
       <c r="I17" s="14"/>
     </row>
     <row r="18" spans="2:9" ht="18" customHeight="1">
@@ -1053,13 +1053,13 @@
       <c r="C18" s="8">
         <v>0</v>
       </c>
-      <c r="D18" s="17" t="s">
+      <c r="D18" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="E18" s="18"/>
-      <c r="F18" s="18"/>
-      <c r="G18" s="18"/>
-      <c r="H18" s="19"/>
+      <c r="E18" s="21"/>
+      <c r="F18" s="21"/>
+      <c r="G18" s="21"/>
+      <c r="H18" s="22"/>
       <c r="I18" s="14"/>
     </row>
     <row r="19" spans="2:9" ht="18.75" customHeight="1">
@@ -1069,13 +1069,13 @@
       <c r="C19" s="8">
         <v>0</v>
       </c>
-      <c r="D19" s="17" t="s">
+      <c r="D19" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="E19" s="18"/>
-      <c r="F19" s="18"/>
-      <c r="G19" s="18"/>
-      <c r="H19" s="19"/>
+      <c r="E19" s="21"/>
+      <c r="F19" s="21"/>
+      <c r="G19" s="21"/>
+      <c r="H19" s="22"/>
       <c r="I19" s="14"/>
     </row>
     <row r="20" spans="2:9" ht="18" customHeight="1">
@@ -1085,13 +1085,13 @@
       <c r="C20" s="8">
         <v>0</v>
       </c>
-      <c r="D20" s="17" t="s">
+      <c r="D20" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="E20" s="18"/>
-      <c r="F20" s="18"/>
-      <c r="G20" s="18"/>
-      <c r="H20" s="19"/>
+      <c r="E20" s="21"/>
+      <c r="F20" s="21"/>
+      <c r="G20" s="21"/>
+      <c r="H20" s="22"/>
       <c r="I20" s="14"/>
     </row>
     <row r="21" spans="2:9" ht="18.75" customHeight="1">
@@ -1101,13 +1101,13 @@
       <c r="C21" s="8">
         <v>0</v>
       </c>
-      <c r="D21" s="17" t="s">
+      <c r="D21" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="E21" s="18"/>
-      <c r="F21" s="18"/>
-      <c r="G21" s="18"/>
-      <c r="H21" s="19"/>
+      <c r="E21" s="21"/>
+      <c r="F21" s="21"/>
+      <c r="G21" s="21"/>
+      <c r="H21" s="22"/>
       <c r="I21" s="14"/>
     </row>
     <row r="22" spans="2:9" ht="21.75" customHeight="1">
@@ -1117,13 +1117,13 @@
       <c r="C22" s="8">
         <v>0</v>
       </c>
-      <c r="D22" s="17" t="s">
+      <c r="D22" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="E22" s="18"/>
-      <c r="F22" s="18"/>
-      <c r="G22" s="18"/>
-      <c r="H22" s="19"/>
+      <c r="E22" s="21"/>
+      <c r="F22" s="21"/>
+      <c r="G22" s="21"/>
+      <c r="H22" s="22"/>
       <c r="I22" s="14"/>
     </row>
     <row r="23" spans="2:9" ht="21" customHeight="1">
@@ -1133,13 +1133,13 @@
       <c r="C23" s="8">
         <v>0</v>
       </c>
-      <c r="D23" s="17" t="s">
+      <c r="D23" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="E23" s="18"/>
-      <c r="F23" s="18"/>
-      <c r="G23" s="18"/>
-      <c r="H23" s="19"/>
+      <c r="E23" s="21"/>
+      <c r="F23" s="21"/>
+      <c r="G23" s="21"/>
+      <c r="H23" s="22"/>
       <c r="I23" s="14"/>
     </row>
     <row r="24" spans="2:9" ht="75" customHeight="1">
@@ -1149,13 +1149,13 @@
       <c r="C24" s="8">
         <v>8.5</v>
       </c>
-      <c r="D24" s="17" t="s">
+      <c r="D24" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="E24" s="18"/>
-      <c r="F24" s="18"/>
-      <c r="G24" s="18"/>
-      <c r="H24" s="19"/>
+      <c r="E24" s="21"/>
+      <c r="F24" s="21"/>
+      <c r="G24" s="21"/>
+      <c r="H24" s="22"/>
       <c r="I24" s="14"/>
     </row>
     <row r="25" spans="2:9" ht="104.25" customHeight="1">
@@ -1165,13 +1165,13 @@
       <c r="C25" s="8">
         <v>8.5</v>
       </c>
-      <c r="D25" s="17" t="s">
+      <c r="D25" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="E25" s="18"/>
-      <c r="F25" s="18"/>
-      <c r="G25" s="18"/>
-      <c r="H25" s="19"/>
+      <c r="E25" s="21"/>
+      <c r="F25" s="21"/>
+      <c r="G25" s="21"/>
+      <c r="H25" s="22"/>
       <c r="I25" s="14"/>
     </row>
     <row r="26" spans="2:9" ht="69" customHeight="1">
@@ -1181,13 +1181,13 @@
       <c r="C26" s="8">
         <v>8.5</v>
       </c>
-      <c r="D26" s="17" t="s">
+      <c r="D26" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="E26" s="18"/>
-      <c r="F26" s="18"/>
-      <c r="G26" s="18"/>
-      <c r="H26" s="19"/>
+      <c r="E26" s="21"/>
+      <c r="F26" s="21"/>
+      <c r="G26" s="21"/>
+      <c r="H26" s="22"/>
       <c r="I26" s="14"/>
     </row>
     <row r="27" spans="2:9" ht="72.75" customHeight="1">
@@ -1197,13 +1197,13 @@
       <c r="C27" s="8">
         <v>8.5</v>
       </c>
-      <c r="D27" s="17" t="s">
+      <c r="D27" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="E27" s="18"/>
-      <c r="F27" s="18"/>
-      <c r="G27" s="18"/>
-      <c r="H27" s="19"/>
+      <c r="E27" s="21"/>
+      <c r="F27" s="21"/>
+      <c r="G27" s="21"/>
+      <c r="H27" s="22"/>
       <c r="I27" s="14"/>
     </row>
     <row r="28" spans="2:9" ht="69.75" customHeight="1">
@@ -1213,13 +1213,13 @@
       <c r="C28" s="8">
         <v>8.5</v>
       </c>
-      <c r="D28" s="17" t="s">
+      <c r="D28" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="E28" s="18"/>
-      <c r="F28" s="18"/>
-      <c r="G28" s="18"/>
-      <c r="H28" s="19"/>
+      <c r="E28" s="21"/>
+      <c r="F28" s="21"/>
+      <c r="G28" s="21"/>
+      <c r="H28" s="22"/>
       <c r="I28" s="14"/>
     </row>
     <row r="29" spans="2:9" ht="18.75" customHeight="1">
@@ -1229,13 +1229,13 @@
       <c r="C29" s="8">
         <v>0</v>
       </c>
-      <c r="D29" s="17" t="s">
+      <c r="D29" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="E29" s="18"/>
-      <c r="F29" s="18"/>
-      <c r="G29" s="18"/>
-      <c r="H29" s="19"/>
+      <c r="E29" s="21"/>
+      <c r="F29" s="21"/>
+      <c r="G29" s="21"/>
+      <c r="H29" s="22"/>
       <c r="I29" s="14"/>
     </row>
     <row r="30" spans="2:9" ht="21.75" customHeight="1">
@@ -1245,13 +1245,13 @@
       <c r="C30" s="8">
         <v>0</v>
       </c>
-      <c r="D30" s="17" t="s">
+      <c r="D30" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="E30" s="18"/>
-      <c r="F30" s="18"/>
-      <c r="G30" s="18"/>
-      <c r="H30" s="19"/>
+      <c r="E30" s="21"/>
+      <c r="F30" s="21"/>
+      <c r="G30" s="21"/>
+      <c r="H30" s="22"/>
       <c r="I30" s="14"/>
     </row>
     <row r="31" spans="2:9" ht="65.25" customHeight="1">
@@ -1261,13 +1261,13 @@
       <c r="C31" s="8">
         <v>8.5</v>
       </c>
-      <c r="D31" s="17" t="s">
+      <c r="D31" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="E31" s="18"/>
-      <c r="F31" s="18"/>
-      <c r="G31" s="18"/>
-      <c r="H31" s="19"/>
+      <c r="E31" s="21"/>
+      <c r="F31" s="21"/>
+      <c r="G31" s="21"/>
+      <c r="H31" s="22"/>
       <c r="I31" s="14"/>
     </row>
     <row r="32" spans="2:9" ht="76.5" customHeight="1">
@@ -1277,13 +1277,13 @@
       <c r="C32" s="8">
         <v>8.5</v>
       </c>
-      <c r="D32" s="17" t="s">
+      <c r="D32" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="E32" s="18"/>
-      <c r="F32" s="18"/>
-      <c r="G32" s="18"/>
-      <c r="H32" s="19"/>
+      <c r="E32" s="21"/>
+      <c r="F32" s="21"/>
+      <c r="G32" s="21"/>
+      <c r="H32" s="22"/>
       <c r="I32" s="14"/>
     </row>
     <row r="33" spans="2:9" ht="78" customHeight="1">
@@ -1293,13 +1293,13 @@
       <c r="C33" s="8">
         <v>8.5</v>
       </c>
-      <c r="D33" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="E33" s="18"/>
-      <c r="F33" s="18"/>
-      <c r="G33" s="18"/>
-      <c r="H33" s="19"/>
+      <c r="D33" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="E33" s="21"/>
+      <c r="F33" s="21"/>
+      <c r="G33" s="21"/>
+      <c r="H33" s="22"/>
       <c r="I33" s="14"/>
     </row>
     <row r="34" spans="2:9" ht="79.5" customHeight="1">
@@ -1309,13 +1309,13 @@
       <c r="C34" s="8">
         <v>8.5</v>
       </c>
-      <c r="D34" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="E34" s="18"/>
-      <c r="F34" s="18"/>
-      <c r="G34" s="18"/>
-      <c r="H34" s="19"/>
+      <c r="D34" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="E34" s="21"/>
+      <c r="F34" s="21"/>
+      <c r="G34" s="21"/>
+      <c r="H34" s="22"/>
       <c r="I34" s="14"/>
     </row>
     <row r="35" spans="2:9" ht="93" customHeight="1">
@@ -1325,13 +1325,13 @@
       <c r="C35" s="8">
         <v>8.5</v>
       </c>
-      <c r="D35" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="E35" s="18"/>
-      <c r="F35" s="18"/>
-      <c r="G35" s="18"/>
-      <c r="H35" s="19"/>
+      <c r="D35" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="E35" s="21"/>
+      <c r="F35" s="21"/>
+      <c r="G35" s="21"/>
+      <c r="H35" s="22"/>
       <c r="I35" s="14"/>
     </row>
     <row r="36" spans="2:9" ht="24.75" customHeight="1">
@@ -1341,13 +1341,13 @@
       <c r="C36" s="8">
         <v>0</v>
       </c>
-      <c r="D36" s="17" t="s">
+      <c r="D36" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="E36" s="18"/>
-      <c r="F36" s="18"/>
-      <c r="G36" s="18"/>
-      <c r="H36" s="19"/>
+      <c r="E36" s="21"/>
+      <c r="F36" s="21"/>
+      <c r="G36" s="21"/>
+      <c r="H36" s="22"/>
       <c r="I36" s="14"/>
     </row>
     <row r="37" spans="2:9" ht="28.5" customHeight="1">
@@ -1357,13 +1357,13 @@
       <c r="C37" s="8">
         <v>0</v>
       </c>
-      <c r="D37" s="32" t="s">
+      <c r="D37" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="E37" s="33"/>
-      <c r="F37" s="33"/>
-      <c r="G37" s="33"/>
-      <c r="H37" s="34"/>
+      <c r="E37" s="18"/>
+      <c r="F37" s="18"/>
+      <c r="G37" s="18"/>
+      <c r="H37" s="19"/>
       <c r="I37" s="14"/>
     </row>
     <row r="38" spans="2:9" ht="74.25" customHeight="1">
@@ -1373,13 +1373,13 @@
       <c r="C38" s="8">
         <v>8.5</v>
       </c>
-      <c r="D38" s="32" t="s">
-        <v>36</v>
-      </c>
-      <c r="E38" s="33"/>
-      <c r="F38" s="33"/>
-      <c r="G38" s="33"/>
-      <c r="H38" s="34"/>
+      <c r="D38" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="E38" s="18"/>
+      <c r="F38" s="18"/>
+      <c r="G38" s="18"/>
+      <c r="H38" s="19"/>
       <c r="I38" s="14"/>
     </row>
     <row r="39" spans="2:9" ht="30" customHeight="1">
@@ -1390,19 +1390,19 @@
         <f>SUM(C9:C38)</f>
         <v>136</v>
       </c>
-      <c r="D39" s="31" t="s">
+      <c r="D39" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="E39" s="31"/>
-      <c r="F39" s="31"/>
-      <c r="G39" s="31"/>
-      <c r="H39" s="31"/>
+      <c r="E39" s="25"/>
+      <c r="F39" s="25"/>
+      <c r="G39" s="25"/>
+      <c r="H39" s="25"/>
     </row>
     <row r="41" spans="2:9" ht="30" customHeight="1">
-      <c r="B41" s="30" t="s">
+      <c r="B41" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="C41" s="30"/>
+      <c r="C41" s="23"/>
       <c r="D41" s="24"/>
       <c r="E41" s="24"/>
       <c r="F41" s="24"/>
@@ -1417,10 +1417,10 @@
       <c r="B42" s="12"/>
     </row>
     <row r="43" spans="2:9" ht="30" customHeight="1">
-      <c r="B43" s="30" t="s">
+      <c r="B43" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="C43" s="30"/>
+      <c r="C43" s="23"/>
       <c r="D43" s="24"/>
       <c r="E43" s="24"/>
       <c r="F43" s="24"/>
@@ -1433,10 +1433,10 @@
       <c r="B44" s="12"/>
     </row>
     <row r="45" spans="2:9" ht="30" customHeight="1">
-      <c r="B45" s="30" t="s">
+      <c r="B45" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="C45" s="30"/>
+      <c r="C45" s="23"/>
       <c r="D45" s="24"/>
       <c r="E45" s="24"/>
       <c r="F45" s="24"/>
@@ -1447,6 +1447,32 @@
     </row>
   </sheetData>
   <mergeCells count="42">
+    <mergeCell ref="D27:H27"/>
+    <mergeCell ref="D17:H17"/>
+    <mergeCell ref="D18:H18"/>
+    <mergeCell ref="D19:H19"/>
+    <mergeCell ref="D20:H20"/>
+    <mergeCell ref="D21:H21"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="D16:H16"/>
+    <mergeCell ref="D10:H10"/>
+    <mergeCell ref="D11:H11"/>
+    <mergeCell ref="D12:H12"/>
+    <mergeCell ref="D13:H13"/>
+    <mergeCell ref="D14:H14"/>
+    <mergeCell ref="D9:H9"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="D8:H8"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="D43:F43"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="D45:F45"/>
+    <mergeCell ref="D39:H39"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="D41:F41"/>
     <mergeCell ref="D38:H38"/>
     <mergeCell ref="D28:H28"/>
     <mergeCell ref="D29:H29"/>
@@ -1463,32 +1489,6 @@
     <mergeCell ref="D37:H37"/>
     <mergeCell ref="D25:H25"/>
     <mergeCell ref="D26:H26"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="D43:F43"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="D45:F45"/>
-    <mergeCell ref="D39:H39"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="D41:F41"/>
-    <mergeCell ref="D9:H9"/>
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="C4:E4"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="D8:H8"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="D16:H16"/>
-    <mergeCell ref="D10:H10"/>
-    <mergeCell ref="D11:H11"/>
-    <mergeCell ref="D12:H12"/>
-    <mergeCell ref="D13:H13"/>
-    <mergeCell ref="D14:H14"/>
-    <mergeCell ref="D27:H27"/>
-    <mergeCell ref="D17:H17"/>
-    <mergeCell ref="D18:H18"/>
-    <mergeCell ref="D19:H19"/>
-    <mergeCell ref="D20:H20"/>
-    <mergeCell ref="D21:H21"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <hyperlinks>
@@ -1502,9 +1502,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1622,19 +1625,15 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2557F9BC-8CE0-4467-BBA0-44089D18E7E7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3DBB90D6-6CF2-454A-903E-412076510F41}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1656,9 +1655,10 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3DBB90D6-6CF2-454A-903E-412076510F41}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2557F9BC-8CE0-4467-BBA0-44089D18E7E7}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Hemapreetha_Timesheet_1June-30June.xlsx
+++ b/Hemapreetha_Timesheet_1June-30June.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gunas\Hema\git-my\vinove\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{801A7756-0FBF-45C7-B5DF-AE922CE38056}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D09E01B7-B371-4FA3-AE78-88B53D1C7FA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="38">
   <si>
     <t>Monthly Timesheet</t>
   </si>
@@ -195,6 +195,9 @@
 ============
 Product Backlog Item 504531: PT-2409 - ZIL Factsheet Migration +Docs - Theme amendments
 Product Backlog Item 462523: PT-2701 - Valiant Bank - ESG Report Design Updates</t>
+  </si>
+  <si>
+    <t>Limited Leave</t>
   </si>
 </sst>
 </file>
@@ -432,15 +435,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="15" fontId="1" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="1" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="1" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="1" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="15" fontId="1" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -449,23 +443,20 @@
     <xf numFmtId="15" fontId="1" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="164" fontId="1" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="3"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="3"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -480,8 +471,20 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="1" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="1" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="1" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -832,15 +835,15 @@
   <sheetData>
     <row r="1" spans="2:9" ht="17.25" thickBot="1"/>
     <row r="2" spans="2:9" ht="59.1" customHeight="1" thickTop="1" thickBot="1">
-      <c r="B2" s="26" t="s">
+      <c r="B2" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
-      <c r="H2" s="28"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="23"/>
     </row>
     <row r="4" spans="2:9" ht="30" customHeight="1">
       <c r="B4" s="3" t="s">
@@ -862,11 +865,11 @@
       <c r="B5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="29">
+      <c r="C5" s="25">
         <v>9025475571</v>
       </c>
-      <c r="D5" s="29"/>
-      <c r="E5" s="29"/>
+      <c r="D5" s="25"/>
+      <c r="E5" s="25"/>
       <c r="G5" s="3" t="s">
         <v>4</v>
       </c>
@@ -878,11 +881,11 @@
       <c r="B6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="30" t="s">
+      <c r="C6" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="30"/>
-      <c r="E6" s="30"/>
+      <c r="D6" s="26"/>
+      <c r="E6" s="26"/>
     </row>
     <row r="8" spans="2:9" ht="30" customHeight="1">
       <c r="B8" s="5" t="s">
@@ -891,13 +894,13 @@
       <c r="C8" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="31" t="s">
+      <c r="D8" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="32"/>
-      <c r="F8" s="32"/>
-      <c r="G8" s="32"/>
-      <c r="H8" s="33"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="29"/>
       <c r="I8" s="7" t="s">
         <v>9</v>
       </c>
@@ -909,13 +912,13 @@
       <c r="C9" s="8">
         <v>0</v>
       </c>
-      <c r="D9" s="20" t="s">
+      <c r="D9" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="E9" s="21"/>
-      <c r="F9" s="21"/>
-      <c r="G9" s="21"/>
-      <c r="H9" s="22"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="18"/>
+      <c r="H9" s="19"/>
       <c r="I9" s="14"/>
     </row>
     <row r="10" spans="2:9" ht="88.5" customHeight="1">
@@ -925,13 +928,13 @@
       <c r="C10" s="8">
         <v>8.5</v>
       </c>
-      <c r="D10" s="20" t="s">
+      <c r="D10" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="E10" s="21"/>
-      <c r="F10" s="21"/>
-      <c r="G10" s="21"/>
-      <c r="H10" s="22"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
+      <c r="G10" s="18"/>
+      <c r="H10" s="19"/>
       <c r="I10" s="14"/>
     </row>
     <row r="11" spans="2:9" ht="72" customHeight="1">
@@ -941,13 +944,13 @@
       <c r="C11" s="8">
         <v>8.5</v>
       </c>
-      <c r="D11" s="34" t="s">
+      <c r="D11" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="E11" s="21"/>
-      <c r="F11" s="21"/>
-      <c r="G11" s="21"/>
-      <c r="H11" s="22"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="18"/>
+      <c r="H11" s="19"/>
       <c r="I11" s="14"/>
     </row>
     <row r="12" spans="2:9" ht="90.75" customHeight="1">
@@ -957,13 +960,13 @@
       <c r="C12" s="8">
         <v>8.5</v>
       </c>
-      <c r="D12" s="20" t="s">
+      <c r="D12" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="E12" s="21"/>
-      <c r="F12" s="21"/>
-      <c r="G12" s="21"/>
-      <c r="H12" s="22"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
+      <c r="G12" s="18"/>
+      <c r="H12" s="19"/>
       <c r="I12" s="14"/>
     </row>
     <row r="13" spans="2:9" ht="72.75" customHeight="1">
@@ -973,13 +976,13 @@
       <c r="C13" s="8">
         <v>8.5</v>
       </c>
-      <c r="D13" s="20" t="s">
+      <c r="D13" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="E13" s="21"/>
-      <c r="F13" s="21"/>
-      <c r="G13" s="21"/>
-      <c r="H13" s="22"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
+      <c r="G13" s="18"/>
+      <c r="H13" s="19"/>
       <c r="I13" s="14"/>
     </row>
     <row r="14" spans="2:9" ht="86.25" customHeight="1">
@@ -989,13 +992,13 @@
       <c r="C14" s="8">
         <v>8.5</v>
       </c>
-      <c r="D14" s="20" t="s">
+      <c r="D14" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="E14" s="21"/>
-      <c r="F14" s="21"/>
-      <c r="G14" s="21"/>
-      <c r="H14" s="22"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="18"/>
+      <c r="G14" s="18"/>
+      <c r="H14" s="19"/>
       <c r="I14" s="14"/>
     </row>
     <row r="15" spans="2:9" ht="17.25" customHeight="1">
@@ -1005,13 +1008,13 @@
       <c r="C15" s="8">
         <v>0</v>
       </c>
-      <c r="D15" s="20" t="s">
+      <c r="D15" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="E15" s="21"/>
-      <c r="F15" s="21"/>
-      <c r="G15" s="21"/>
-      <c r="H15" s="22"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="18"/>
+      <c r="H15" s="19"/>
       <c r="I15" s="14"/>
     </row>
     <row r="16" spans="2:9" ht="21" customHeight="1">
@@ -1021,13 +1024,13 @@
       <c r="C16" s="8">
         <v>0</v>
       </c>
-      <c r="D16" s="20" t="s">
+      <c r="D16" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="E16" s="21"/>
-      <c r="F16" s="21"/>
-      <c r="G16" s="21"/>
-      <c r="H16" s="22"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="18"/>
+      <c r="G16" s="18"/>
+      <c r="H16" s="19"/>
       <c r="I16" s="14"/>
     </row>
     <row r="17" spans="2:9" ht="18" customHeight="1">
@@ -1037,13 +1040,13 @@
       <c r="C17" s="8">
         <v>0</v>
       </c>
-      <c r="D17" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="E17" s="21"/>
-      <c r="F17" s="21"/>
-      <c r="G17" s="21"/>
-      <c r="H17" s="22"/>
+      <c r="D17" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="E17" s="18"/>
+      <c r="F17" s="18"/>
+      <c r="G17" s="18"/>
+      <c r="H17" s="19"/>
       <c r="I17" s="14"/>
     </row>
     <row r="18" spans="2:9" ht="18" customHeight="1">
@@ -1053,13 +1056,13 @@
       <c r="C18" s="8">
         <v>0</v>
       </c>
-      <c r="D18" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="E18" s="21"/>
-      <c r="F18" s="21"/>
-      <c r="G18" s="21"/>
-      <c r="H18" s="22"/>
+      <c r="D18" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="E18" s="18"/>
+      <c r="F18" s="18"/>
+      <c r="G18" s="18"/>
+      <c r="H18" s="19"/>
       <c r="I18" s="14"/>
     </row>
     <row r="19" spans="2:9" ht="18.75" customHeight="1">
@@ -1069,13 +1072,13 @@
       <c r="C19" s="8">
         <v>0</v>
       </c>
-      <c r="D19" s="20" t="s">
+      <c r="D19" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="E19" s="21"/>
-      <c r="F19" s="21"/>
-      <c r="G19" s="21"/>
-      <c r="H19" s="22"/>
+      <c r="E19" s="18"/>
+      <c r="F19" s="18"/>
+      <c r="G19" s="18"/>
+      <c r="H19" s="19"/>
       <c r="I19" s="14"/>
     </row>
     <row r="20" spans="2:9" ht="18" customHeight="1">
@@ -1085,13 +1088,13 @@
       <c r="C20" s="8">
         <v>0</v>
       </c>
-      <c r="D20" s="20" t="s">
+      <c r="D20" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="E20" s="21"/>
-      <c r="F20" s="21"/>
-      <c r="G20" s="21"/>
-      <c r="H20" s="22"/>
+      <c r="E20" s="18"/>
+      <c r="F20" s="18"/>
+      <c r="G20" s="18"/>
+      <c r="H20" s="19"/>
       <c r="I20" s="14"/>
     </row>
     <row r="21" spans="2:9" ht="18.75" customHeight="1">
@@ -1101,13 +1104,13 @@
       <c r="C21" s="8">
         <v>0</v>
       </c>
-      <c r="D21" s="20" t="s">
+      <c r="D21" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="E21" s="21"/>
-      <c r="F21" s="21"/>
-      <c r="G21" s="21"/>
-      <c r="H21" s="22"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="18"/>
+      <c r="G21" s="18"/>
+      <c r="H21" s="19"/>
       <c r="I21" s="14"/>
     </row>
     <row r="22" spans="2:9" ht="21.75" customHeight="1">
@@ -1117,13 +1120,13 @@
       <c r="C22" s="8">
         <v>0</v>
       </c>
-      <c r="D22" s="20" t="s">
+      <c r="D22" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="E22" s="21"/>
-      <c r="F22" s="21"/>
-      <c r="G22" s="21"/>
-      <c r="H22" s="22"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="18"/>
+      <c r="H22" s="19"/>
       <c r="I22" s="14"/>
     </row>
     <row r="23" spans="2:9" ht="21" customHeight="1">
@@ -1133,13 +1136,13 @@
       <c r="C23" s="8">
         <v>0</v>
       </c>
-      <c r="D23" s="20" t="s">
+      <c r="D23" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="E23" s="21"/>
-      <c r="F23" s="21"/>
-      <c r="G23" s="21"/>
-      <c r="H23" s="22"/>
+      <c r="E23" s="18"/>
+      <c r="F23" s="18"/>
+      <c r="G23" s="18"/>
+      <c r="H23" s="19"/>
       <c r="I23" s="14"/>
     </row>
     <row r="24" spans="2:9" ht="75" customHeight="1">
@@ -1149,13 +1152,13 @@
       <c r="C24" s="8">
         <v>8.5</v>
       </c>
-      <c r="D24" s="20" t="s">
+      <c r="D24" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="E24" s="21"/>
-      <c r="F24" s="21"/>
-      <c r="G24" s="21"/>
-      <c r="H24" s="22"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="18"/>
+      <c r="H24" s="19"/>
       <c r="I24" s="14"/>
     </row>
     <row r="25" spans="2:9" ht="104.25" customHeight="1">
@@ -1165,13 +1168,13 @@
       <c r="C25" s="8">
         <v>8.5</v>
       </c>
-      <c r="D25" s="20" t="s">
+      <c r="D25" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="E25" s="21"/>
-      <c r="F25" s="21"/>
-      <c r="G25" s="21"/>
-      <c r="H25" s="22"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="18"/>
+      <c r="G25" s="18"/>
+      <c r="H25" s="19"/>
       <c r="I25" s="14"/>
     </row>
     <row r="26" spans="2:9" ht="69" customHeight="1">
@@ -1181,13 +1184,13 @@
       <c r="C26" s="8">
         <v>8.5</v>
       </c>
-      <c r="D26" s="20" t="s">
+      <c r="D26" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="E26" s="21"/>
-      <c r="F26" s="21"/>
-      <c r="G26" s="21"/>
-      <c r="H26" s="22"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="18"/>
+      <c r="G26" s="18"/>
+      <c r="H26" s="19"/>
       <c r="I26" s="14"/>
     </row>
     <row r="27" spans="2:9" ht="72.75" customHeight="1">
@@ -1197,13 +1200,13 @@
       <c r="C27" s="8">
         <v>8.5</v>
       </c>
-      <c r="D27" s="20" t="s">
+      <c r="D27" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="E27" s="21"/>
-      <c r="F27" s="21"/>
-      <c r="G27" s="21"/>
-      <c r="H27" s="22"/>
+      <c r="E27" s="18"/>
+      <c r="F27" s="18"/>
+      <c r="G27" s="18"/>
+      <c r="H27" s="19"/>
       <c r="I27" s="14"/>
     </row>
     <row r="28" spans="2:9" ht="69.75" customHeight="1">
@@ -1213,13 +1216,13 @@
       <c r="C28" s="8">
         <v>8.5</v>
       </c>
-      <c r="D28" s="20" t="s">
+      <c r="D28" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="E28" s="21"/>
-      <c r="F28" s="21"/>
-      <c r="G28" s="21"/>
-      <c r="H28" s="22"/>
+      <c r="E28" s="18"/>
+      <c r="F28" s="18"/>
+      <c r="G28" s="18"/>
+      <c r="H28" s="19"/>
       <c r="I28" s="14"/>
     </row>
     <row r="29" spans="2:9" ht="18.75" customHeight="1">
@@ -1229,13 +1232,13 @@
       <c r="C29" s="8">
         <v>0</v>
       </c>
-      <c r="D29" s="20" t="s">
+      <c r="D29" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="E29" s="21"/>
-      <c r="F29" s="21"/>
-      <c r="G29" s="21"/>
-      <c r="H29" s="22"/>
+      <c r="E29" s="18"/>
+      <c r="F29" s="18"/>
+      <c r="G29" s="18"/>
+      <c r="H29" s="19"/>
       <c r="I29" s="14"/>
     </row>
     <row r="30" spans="2:9" ht="21.75" customHeight="1">
@@ -1245,13 +1248,13 @@
       <c r="C30" s="8">
         <v>0</v>
       </c>
-      <c r="D30" s="20" t="s">
+      <c r="D30" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="E30" s="21"/>
-      <c r="F30" s="21"/>
-      <c r="G30" s="21"/>
-      <c r="H30" s="22"/>
+      <c r="E30" s="18"/>
+      <c r="F30" s="18"/>
+      <c r="G30" s="18"/>
+      <c r="H30" s="19"/>
       <c r="I30" s="14"/>
     </row>
     <row r="31" spans="2:9" ht="65.25" customHeight="1">
@@ -1261,13 +1264,13 @@
       <c r="C31" s="8">
         <v>8.5</v>
       </c>
-      <c r="D31" s="20" t="s">
+      <c r="D31" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="E31" s="21"/>
-      <c r="F31" s="21"/>
-      <c r="G31" s="21"/>
-      <c r="H31" s="22"/>
+      <c r="E31" s="18"/>
+      <c r="F31" s="18"/>
+      <c r="G31" s="18"/>
+      <c r="H31" s="19"/>
       <c r="I31" s="14"/>
     </row>
     <row r="32" spans="2:9" ht="76.5" customHeight="1">
@@ -1277,13 +1280,13 @@
       <c r="C32" s="8">
         <v>8.5</v>
       </c>
-      <c r="D32" s="20" t="s">
+      <c r="D32" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="E32" s="21"/>
-      <c r="F32" s="21"/>
-      <c r="G32" s="21"/>
-      <c r="H32" s="22"/>
+      <c r="E32" s="18"/>
+      <c r="F32" s="18"/>
+      <c r="G32" s="18"/>
+      <c r="H32" s="19"/>
       <c r="I32" s="14"/>
     </row>
     <row r="33" spans="2:9" ht="78" customHeight="1">
@@ -1293,13 +1296,13 @@
       <c r="C33" s="8">
         <v>8.5</v>
       </c>
-      <c r="D33" s="20" t="s">
+      <c r="D33" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="E33" s="21"/>
-      <c r="F33" s="21"/>
-      <c r="G33" s="21"/>
-      <c r="H33" s="22"/>
+      <c r="E33" s="18"/>
+      <c r="F33" s="18"/>
+      <c r="G33" s="18"/>
+      <c r="H33" s="19"/>
       <c r="I33" s="14"/>
     </row>
     <row r="34" spans="2:9" ht="79.5" customHeight="1">
@@ -1309,13 +1312,13 @@
       <c r="C34" s="8">
         <v>8.5</v>
       </c>
-      <c r="D34" s="20" t="s">
+      <c r="D34" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="E34" s="21"/>
-      <c r="F34" s="21"/>
-      <c r="G34" s="21"/>
-      <c r="H34" s="22"/>
+      <c r="E34" s="18"/>
+      <c r="F34" s="18"/>
+      <c r="G34" s="18"/>
+      <c r="H34" s="19"/>
       <c r="I34" s="14"/>
     </row>
     <row r="35" spans="2:9" ht="93" customHeight="1">
@@ -1325,13 +1328,13 @@
       <c r="C35" s="8">
         <v>8.5</v>
       </c>
-      <c r="D35" s="20" t="s">
+      <c r="D35" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="E35" s="21"/>
-      <c r="F35" s="21"/>
-      <c r="G35" s="21"/>
-      <c r="H35" s="22"/>
+      <c r="E35" s="18"/>
+      <c r="F35" s="18"/>
+      <c r="G35" s="18"/>
+      <c r="H35" s="19"/>
       <c r="I35" s="14"/>
     </row>
     <row r="36" spans="2:9" ht="24.75" customHeight="1">
@@ -1341,13 +1344,13 @@
       <c r="C36" s="8">
         <v>0</v>
       </c>
-      <c r="D36" s="20" t="s">
+      <c r="D36" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="E36" s="21"/>
-      <c r="F36" s="21"/>
-      <c r="G36" s="21"/>
-      <c r="H36" s="22"/>
+      <c r="E36" s="18"/>
+      <c r="F36" s="18"/>
+      <c r="G36" s="18"/>
+      <c r="H36" s="19"/>
       <c r="I36" s="14"/>
     </row>
     <row r="37" spans="2:9" ht="28.5" customHeight="1">
@@ -1357,13 +1360,13 @@
       <c r="C37" s="8">
         <v>0</v>
       </c>
-      <c r="D37" s="17" t="s">
+      <c r="D37" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="E37" s="18"/>
-      <c r="F37" s="18"/>
-      <c r="G37" s="18"/>
-      <c r="H37" s="19"/>
+      <c r="E37" s="33"/>
+      <c r="F37" s="33"/>
+      <c r="G37" s="33"/>
+      <c r="H37" s="34"/>
       <c r="I37" s="14"/>
     </row>
     <row r="38" spans="2:9" ht="74.25" customHeight="1">
@@ -1373,13 +1376,13 @@
       <c r="C38" s="8">
         <v>8.5</v>
       </c>
-      <c r="D38" s="17" t="s">
+      <c r="D38" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="E38" s="18"/>
-      <c r="F38" s="18"/>
-      <c r="G38" s="18"/>
-      <c r="H38" s="19"/>
+      <c r="E38" s="33"/>
+      <c r="F38" s="33"/>
+      <c r="G38" s="33"/>
+      <c r="H38" s="34"/>
       <c r="I38" s="14"/>
     </row>
     <row r="39" spans="2:9" ht="30" customHeight="1">
@@ -1390,19 +1393,19 @@
         <f>SUM(C9:C38)</f>
         <v>136</v>
       </c>
-      <c r="D39" s="25" t="s">
+      <c r="D39" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="E39" s="25"/>
-      <c r="F39" s="25"/>
-      <c r="G39" s="25"/>
-      <c r="H39" s="25"/>
+      <c r="E39" s="31"/>
+      <c r="F39" s="31"/>
+      <c r="G39" s="31"/>
+      <c r="H39" s="31"/>
     </row>
     <row r="41" spans="2:9" ht="30" customHeight="1">
-      <c r="B41" s="23" t="s">
+      <c r="B41" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="C41" s="23"/>
+      <c r="C41" s="30"/>
       <c r="D41" s="24"/>
       <c r="E41" s="24"/>
       <c r="F41" s="24"/>
@@ -1417,10 +1420,10 @@
       <c r="B42" s="12"/>
     </row>
     <row r="43" spans="2:9" ht="30" customHeight="1">
-      <c r="B43" s="23" t="s">
+      <c r="B43" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="C43" s="23"/>
+      <c r="C43" s="30"/>
       <c r="D43" s="24"/>
       <c r="E43" s="24"/>
       <c r="F43" s="24"/>
@@ -1433,10 +1436,10 @@
       <c r="B44" s="12"/>
     </row>
     <row r="45" spans="2:9" ht="30" customHeight="1">
-      <c r="B45" s="23" t="s">
+      <c r="B45" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="C45" s="23"/>
+      <c r="C45" s="30"/>
       <c r="D45" s="24"/>
       <c r="E45" s="24"/>
       <c r="F45" s="24"/>
@@ -1447,32 +1450,6 @@
     </row>
   </sheetData>
   <mergeCells count="42">
-    <mergeCell ref="D27:H27"/>
-    <mergeCell ref="D17:H17"/>
-    <mergeCell ref="D18:H18"/>
-    <mergeCell ref="D19:H19"/>
-    <mergeCell ref="D20:H20"/>
-    <mergeCell ref="D21:H21"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="D16:H16"/>
-    <mergeCell ref="D10:H10"/>
-    <mergeCell ref="D11:H11"/>
-    <mergeCell ref="D12:H12"/>
-    <mergeCell ref="D13:H13"/>
-    <mergeCell ref="D14:H14"/>
-    <mergeCell ref="D9:H9"/>
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="C4:E4"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="D8:H8"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="D43:F43"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="D45:F45"/>
-    <mergeCell ref="D39:H39"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="D41:F41"/>
     <mergeCell ref="D38:H38"/>
     <mergeCell ref="D28:H28"/>
     <mergeCell ref="D29:H29"/>
@@ -1489,6 +1466,32 @@
     <mergeCell ref="D37:H37"/>
     <mergeCell ref="D25:H25"/>
     <mergeCell ref="D26:H26"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="D43:F43"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="D45:F45"/>
+    <mergeCell ref="D39:H39"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="D41:F41"/>
+    <mergeCell ref="D9:H9"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="D8:H8"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="D16:H16"/>
+    <mergeCell ref="D10:H10"/>
+    <mergeCell ref="D11:H11"/>
+    <mergeCell ref="D12:H12"/>
+    <mergeCell ref="D13:H13"/>
+    <mergeCell ref="D14:H14"/>
+    <mergeCell ref="D27:H27"/>
+    <mergeCell ref="D17:H17"/>
+    <mergeCell ref="D18:H18"/>
+    <mergeCell ref="D19:H19"/>
+    <mergeCell ref="D20:H20"/>
+    <mergeCell ref="D21:H21"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <hyperlinks>
@@ -1502,12 +1505,9 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1625,15 +1625,19 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3DBB90D6-6CF2-454A-903E-412076510F41}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2557F9BC-8CE0-4467-BBA0-44089D18E7E7}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1655,10 +1659,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2557F9BC-8CE0-4467-BBA0-44089D18E7E7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3DBB90D6-6CF2-454A-903E-412076510F41}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>